--- a/IFE_Matrix_Doner_Street.xlsx
+++ b/IFE_Matrix_Doner_Street.xlsx
@@ -1,172 +1,77 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlo\Desktop\Digitalisierte Ordner\Arbeit und Beruf\Ausbildungs- und Studiensunterlagen\Master Module\3. Semester\Strategic Management\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F13D878-73B6-4004-98D4-A0DDF496222F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="IFE Matrix" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IFE Matrix" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" concurrentCalc="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
-  <si>
-    <t>3.9 Internal Factor Evaluation (IFE) Matrix · Döner Street</t>
-  </si>
-  <si>
-    <t>Weights: 0.0 (not important) to 1.0 (all-important), must sum to 1.00. Ratings: 1 = major weakness, 2 = minor weakness, 3 = minor strength, 4 = major strength (David, Ch. 4). Blue cells are inputs.</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>Key Internal Factors</t>
-  </si>
-  <si>
-    <t>Weight</t>
-  </si>
-  <si>
-    <t>Rating</t>
-  </si>
-  <si>
-    <t>Weighted Score</t>
-  </si>
-  <si>
-    <t>Strengths</t>
-  </si>
-  <si>
-    <t>Fast service with a planned ~2 min assembly per order and ~840 units/day capacity (3.4.2)</t>
-  </si>
-  <si>
-    <t>Store on the Calle 72 corridor next to the new Metro Line 1 and TransMilenio station, a node under redevelopment (Decreto 242/2026) where none of the three rivals is located (2.2.1, 2.5)</t>
-  </si>
-  <si>
-    <t>Healthier than conventional fast food, with fresh lettuce, tomato and onion in every döner and meat roasted on a vertical rotisserie instead of deep-fried (3.4.2)</t>
-  </si>
-  <si>
-    <t>Lean processes around one core product allow fast onboarding, as associates need no degree and learn every station through on-the-job cross-training (3.3.2)</t>
-  </si>
-  <si>
-    <t>Standardized product with defined portions, costs and assembly steps makes the concept easy to replicate at further locations (3.4.2)</t>
-  </si>
-  <si>
-    <t>Weaknesses</t>
-  </si>
-  <si>
-    <t>Unknown brand with no reviews yet vs. Filiák's 4.8 rating (2.5.3)</t>
-  </si>
-  <si>
-    <t>No proprietary recipe, the product follows a standard döner recipe</t>
-  </si>
-  <si>
-    <t>Inexperienced founding team of students aged 18 to 24</t>
-  </si>
-  <si>
-    <t>No operating track record, all sales and marketing figures are forecasts (3.4.5)</t>
-  </si>
-  <si>
-    <t>No own delivery service, so delivery orders depend on aggregator apps charging 18% to 30% commission per order (2.4.1, 3.4.4)</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Interpretation</t>
-  </si>
-  <si>
-    <t>With a total weighted score of 2.48, Döner Street's internal position is just below the average of 2.5. Its main strengths are fast service, a location on the redeveloped Calle 72 corridor and a lean, easily replicable concept. They are offset by the typical weaknesses of a new business, above all an unknown brand, no proprietary recipe and a young founding team without operating history.</t>
-  </si>
-  <si>
-    <t>Source: Fred R. David, Strategic Management, Ch. 4, IFE Matrix; section numbers refer to doner-house-seven.vercel.app</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="8">
     <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
       <name val="Arial"/>
       <charset val="1"/>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
     <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF595959"/>
       <name val="Arial"/>
       <charset val="1"/>
+      <i val="1"/>
+      <color rgb="FF595959"/>
+      <sz val="9"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <charset val="1"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
       <name val="Arial"/>
       <charset val="1"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <charset val="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <charset val="1"/>
+      <color rgb="FF0000FF"/>
+      <sz val="10"/>
     </font>
     <font>
-      <i/>
-      <sz val="8"/>
-      <color rgb="FF808080"/>
       <name val="Arial"/>
       <charset val="1"/>
+      <i val="1"/>
+      <color rgb="FF808080"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -190,7 +95,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -213,55 +118,100 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -331,14 +281,6 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -520,298 +462,381 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="80" customWidth="1"/>
-    <col min="3" max="5" width="14" customWidth="1"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.4">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>3.9 Internal Factor Evaluation (IFE) Matrix · Döner Street</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="27.75" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Weights: 0.0 (not important) to 1.0 (all-important), must sum to 1.00. Ratings: 1 = major weakness, 2 = minor weakness, 3 = minor strength, 4 = major strength (David, Ch. 4). Blue cells are inputs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Key Internal Factors</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Weighted Score</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Strengths</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="18" t="n"/>
+    </row>
+    <row r="6" ht="45" customHeight="1">
+      <c r="A6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="6">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D6" s="9">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Fast service with a planned &gt;2 min assembly per order (Medium Combo, 3.6.1) and ~810 units/day capacity (3.4.2)</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D6" s="9" t="n">
         <v>4</v>
       </c>
       <c r="E6" s="10">
         <f>C6*D6</f>
-        <v>0.56000000000000005</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="6">
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1">
+      <c r="A7" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="8">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Store on the Calle 72 corridor next to the new Metro Line 1 and TransMilenio station, a node under redevelopment (Decreto 242/2026) where none of the three rivals is located (2.2.1, 2.5)</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n">
         <v>0.11</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="9" t="n">
         <v>3</v>
       </c>
       <c r="E7" s="10">
         <f>C7*D7</f>
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="6">
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="8">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Healthier than conventional fast food, with fresh lettuce, tomato and onion in every döner and meat roasted on a vertical rotisserie instead of deep-fried (3.4.2)</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
         <v>0.09</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="9" t="n">
         <v>3</v>
       </c>
       <c r="E8" s="10">
         <f>C8*D8</f>
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="6">
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="8">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="D9" s="9">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Lean processes around one core product allow fast onboarding, as associates need no degree and learn every station through on-the-job cross-training (3.3.2)</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D9" s="9" t="n">
         <v>3</v>
       </c>
       <c r="E9" s="10">
         <f>C9*D9</f>
-        <v>0.21000000000000002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="6">
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="8">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="D10" s="9">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Standardized product with defined portions, costs and assembly steps makes the concept easy to replicate at further locations (3.4.2)</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D10" s="9" t="n">
         <v>3</v>
       </c>
       <c r="E10" s="10">
         <f>C10*D10</f>
-        <v>0.21000000000000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="6">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Weaknesses</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="18" t="n"/>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D12" s="9">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Unknown brand with no reviews yet vs. Filiák's 4.8 rating (2.5.3)</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D12" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E12" s="10">
         <f>C12*D12</f>
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="6">
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="8">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>No proprietary recipe, the product follows a standard döner recipe</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n">
         <v>0.11</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="9" t="n">
         <v>2</v>
       </c>
       <c r="E13" s="10">
         <f>C13*D13</f>
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="6">
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="8">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>No operating track record, all sales and marketing figures are forecasts (3.4.5)</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="9" t="n">
         <v>2</v>
       </c>
       <c r="E14" s="10">
         <f>C14*D14</f>
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="6">
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="D15" s="9">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>No own delivery service, so delivery orders depend on aggregator apps charging 18% to 30% commission per order (2.4.1, 3.4.4)</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D15" s="9" t="n">
         <v>2</v>
       </c>
       <c r="E15" s="10">
         <f>C15*D15</f>
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="6">
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" t="n">
         <v>5</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="8">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="D16" s="9">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Organic content posts only twice a week (Tuesdays &amp; Fridays, 104 days/year), limiting organic reach during the launch ramp-up versus daily-posting rivals (3.4.4)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D16" t="n">
         <v>2</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16">
         <f>C16*D16</f>
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="11"/>
-      <c r="B17" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="13">
-        <f>SUM(C6:C16)</f>
-        <v>1</v>
-      </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="13">
-        <f>SUM(E6:E16)</f>
-        <v>2.4800000000000004</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B18" s="14" t="str">
-        <f>IF(ROUND(C17,2)=1,"Check: weights sum to 1.00","Check: weights must sum to 1.00")</f>
-        <v>Check: weights sum to 1.00</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B19" s="14" t="str">
-        <f>IF(E17&gt;=2.5,"Score at or above the 2.5 average: internal position average to strong","Score below the 2.5 average: internal position slightly weak")</f>
-        <v>Score below the 2.5 average: internal position slightly weak</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="15" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="16" t="s">
-        <v>22</v>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Single Store Manager per store with no assistant, so days off or illness leave shift-level staff handling escalations meant for the store manager (3.3.2, 3.4.3)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <f>C17*D17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>100% equity-funded with no external line of credit, so the pessimistic scenario's forced overdraft has no financing backstop (3.5.1)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18">
+        <f>C18*D18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n"/>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C19" s="13">
+        <f>SUM(C6:C18)</f>
+        <v/>
+      </c>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="13">
+        <f>SUM(E6:E18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="14">
+        <f>IF(ROUND(C19,2)=1,"Check: weights sum to 1.00","Check: weights must sum to 1.00")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="14">
+        <f>IF(E19&gt;=2.5,"Score at or above the 2.5 average: internal position average to strong","Score below the 2.5 average: internal position slightly weak")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1"/>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Interpretation</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>With a total weighted score of 2.48, Döner Street's internal position is just below the average of 2.5. Its main strengths are fast service, a location on the redeveloped Calle 72 corridor and a lean, easily replicable concept. They are offset by the typical weaknesses of a new business, above all an unknown brand, no proprietary recipe and a concentrated marketing/finance risk profile -- twice-weekly organic content, a single Store Manager with no backup, and no external financing cushion -- on top of the same aggregator-commission weakness that drives the delivery commission line in the 3.5.1 Estado de Resultados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Source: Fred R. David, Strategic Management, Ch. 4, IFE Matrix; section numbers refer to doner-house-seven.vercel.app</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A5:E5"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>